--- a/review/etnografiya/may-december/september/september.xlsx
+++ b/review/etnografiya/may-december/september/september.xlsx
@@ -108,7 +108,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что ребёнок несёт из дома в школу?</t>
+          <t xml:space="preserve">Первый ранец собирает школьные вещи в дорожный набор. Учёба становится ежедневным выходом из дома — новый порядок жизни виден в одном предмете.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -135,7 +135,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему старая тетрадь хранит след нажима?</t>
+          <t xml:space="preserve">Перьевая ручка оставляет строку по движению руки. Нажим и направление становятся частью письма: инструмент требует освоенного телесного навыка.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -162,7 +162,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как повтор помогает обрести навык?</t>
+          <t xml:space="preserve">Одинаковые буквы в прописи готовят собственный почерк. Повторение даёт руке уверенность, прежде чем запись начнёт отличаться личным движением.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как сохранить написанное, не размазав его?</t>
+          <t xml:space="preserve">Промокательная бумага помогает ещё мокрой строке. Маленькая школьная принадлежность хранит способ письма, которому требовалось время на высыхание.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -216,7 +216,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как посчитать покупку без записи столбиком?</t>
+          <t xml:space="preserve">На счётах число видно по положению косточек. Движение пальцев меняет запись и расчёт — абстрактное количество получает материальную форму.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -243,7 +243,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему покупателю важно смотреть на гирю?</t>
+          <t xml:space="preserve">Клеймо на гире связано с доверием к мере. Маленький груз участвует в сделке, где покупателю и продавцу важно одинаково понимать вес.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -270,7 +270,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как одно противовесное устройство заменяет две чаши?</t>
+          <t xml:space="preserve">Безмен взвешивает груз на подвеске. Компактное устройство переводит тяжесть вещи в положение, по которому человек узнаёт меру.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -297,7 +297,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему мерка должна быть понятна обеим сторонам?</t>
+          <t xml:space="preserve">Аршином отмеряют ткань для продажи. Будущий наряд начинается с длины полотна — привычная мера связывает торговлю с работой портного.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как найти нужное среди множества торговцев?</t>
+          <t xml:space="preserve">Ярмарочные покупки складываются в путь между рядами. Торговое пространство организует встречу разных нужд, товаров и человеческих занятий.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -351,7 +351,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие слова убеждали покупателя сто лет назад?</t>
+          <t xml:space="preserve">Товарная этикетка обещает качество до открытия упаковки. Надпись и рисунок показывают, как производитель обращается к незнакомому покупателю.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -378,7 +378,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему красивую упаковку не спешат выбрасывать?</t>
+          <t xml:space="preserve">Жестяная коробка остаётся после покупки. Упаковка получает вторую домашнюю жизнь — её содержимое меняется, а след прежнего товара сохраняется.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -405,7 +405,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как вещь помогает откладывать понемногу?</t>
+          <t xml:space="preserve">Копилка собирает небольшие суммы в общий запас. Отдельная монета становится частью будущего решения, которое ещё нельзя оплатить сегодня.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -432,7 +432,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что можно узнать о семье по списку покупок?</t>
+          <t xml:space="preserve">Домашние расходы попадают в тетрадь. Запись делает хозяйство обозримым: деньги связываются с датами, покупками и памятью о сделанном выборе.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -459,7 +459,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему начало осени могло напоминать новый год?</t>
+          <t xml:space="preserve">Семёнов день отмечают особым местным порядком. Встреча осени получает человеческую форму через действия, которые повторяются в годовом круге.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как меняется распорядок, когда темнеет раньше?</t>
+          <t xml:space="preserve">Новая лучина даёт свет для вечерней работы. С наступлением длинных вечеров домашнее ремесло зависит от маленького, постоянно сменяемого огня.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему продукты отправляют вниз?</t>
+          <t xml:space="preserve">Погреб использует прохладу как часть домашнего устройства. Место хранения помогает урожаю пережить сезон, когда свежий сбор уже закончился.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем большой семье большая ёмкость?</t>
+          <t xml:space="preserve">Капустный запас укладывают в кадку слоями. Большая ёмкость собирает множество малых действий — за зимней порцией стоит общая работа заготовки.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему кухонный инструмент похож на маленький полумесяц?</t>
+          <t xml:space="preserve">Сечка рубит капусту особым лезвием. Назначение инструмента видно в его движении: знакомый продукт требует собственной организации работы.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему хлебный день начинается задолго до печи?</t>
+          <t xml:space="preserve">В квашне тесто оставляют подниматься. Хлеб требует не только движения рук, но и ожидания — домашний труд умеет вовремя остановиться.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как сезонная еда остаётся на столе позже?</t>
+          <t xml:space="preserve">Солёные огурцы переносят летний огород в холодный сезон. Заготовка меняет вкус продукта и продлевает путь урожая до семейного стола.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что связывает украшение и знакомый хозяйственный образ?</t>
+          <t xml:space="preserve">Коромысельные серьги напоминают знакомое орудие формой. Бытовое сравнение помогает прочитать устройство украшения, которое носили совсем иначе.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как небольшая вещь становится личной?</t>
+          <t xml:space="preserve">Лента и накосник входят в причёску как подарок. Личная вещь соединяет украшение волос с памятью о человеке, который её преподнёс.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что важнее — вместительность или содержимое?</t>
+          <t xml:space="preserve">Сундук невесты собирает вещи, подготовленные к новой жизни. За наполнением стоит запас семейного труда, который нельзя измерить одним размером сундука.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как семья показывала подготовку к свадьбе?</t>
+          <t xml:space="preserve">Приданое выставляют на обозрение. Ткань, швы и отделка делают мастерство видимым другим людям — домашний труд получает общественную оценку.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как временный заработок меняет домашний календарь?</t>
+          <t xml:space="preserve">Осенний наём выводит работника за пределы деревни. Дорога связывает семейное хозяйство с чужой работой и новым порядком повседневной жизни.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие детали портрета были специально подготовлены?</t>
+          <t xml:space="preserve">В фотоателье человек выбирает, как предстать перед камерой. Костюм, поза и обстановка превращают снимок в подготовленное личное представление.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему календарное название приводит на кухню?</t>
+          <t xml:space="preserve">В народном описании Воздвижения появляются капустные хлопоты. Праздничное имя встречается с сезонной заготовкой семейного стола.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что исчезает, когда фотография остаётся без пояснения?</t>
+          <t xml:space="preserve">Подпись в альбоме сохраняет имя рядом с лицом. Несколько слов могут удержать связь поколений, которую само изображение уже не объясняет.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли восстановить дорогу письма по отметкам?</t>
+          <t xml:space="preserve">Почтовый адрес превращает конверт в маршрут. Имя получателя и название места помогают личному письму пройти через незнакомые руки.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что заплата рассказывает о заботе?</t>
+          <t xml:space="preserve">Осенняя починка даёт одежде ещё один сезон. След ремонта показывает заботу о вещи и умение продолжить её службу вместо немедленной замены.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
